--- a/EXCEL/Classwork/Conditional Formating(Day 2.1)(Data Bars).xlsx
+++ b/EXCEL/Classwork/Conditional Formating(Day 2.1)(Data Bars).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANUDIP_BY_SAYAR_DPBA\EXCEL\Classwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410F2FB7-5EBF-49E9-B73F-7F005F87C69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349A38A9-6182-4D32-A946-70A971610F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -559,10 +559,10 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23769,27 +23769,27 @@
       </c>
       <c r="B3" s="1">
         <f t="shared" ref="B3:B9" ca="1" si="0">RANDBETWEEN(40,100)</f>
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1">
         <f t="shared" ref="C3:D9" ca="1" si="1">RANDBETWEEN(40,100)</f>
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D3" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E3" s="1">
         <f t="shared" ref="E3:E9" ca="1" si="2">SUM(B3:D3)</f>
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="F3" s="1">
         <f t="shared" ref="F3:F9" ca="1" si="3">AVERAGE(B3:D3)</f>
-        <v>62.666666666666664</v>
+        <v>74</v>
       </c>
       <c r="G3" s="1" t="str">
         <f t="shared" ref="G3:G8" ca="1" si="4">IF(F3&gt;=90,"A",IF(F3&gt;=70,"B",IF(F3&gt;=50,"C",IF(F3&gt;=40,"Pass",IF(F3&lt;40,"Fail")))))</f>
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -23798,27 +23798,27 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>69.333333333333329</v>
+        <v>71.666666666666671</v>
       </c>
       <c r="G4" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -23827,27 +23827,27 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="G5" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -23856,27 +23856,27 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>62.333333333333336</v>
+        <v>75.333333333333329</v>
       </c>
       <c r="G6" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -23911,27 +23911,27 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="G8" s="1" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -23940,23 +23940,23 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G9" s="1" t="str">
         <f ca="1">IF(IF9&gt;=90,"A",IF(F9&gt;=70,"B",IF(F9&gt;=50,"C",IF(F9&gt;=40,"Pass",IF(F9&lt;40,"Fail")))))</f>
@@ -90097,14 +90097,14 @@
       <c r="D8" s="1">
         <v>300</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
       <c r="P8" s="1" t="s">
         <v>116</v>
       </c>
@@ -90131,12 +90131,12 @@
       <c r="D9" s="1">
         <v>80</v>
       </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
       <c r="P9" s="1" t="s">
         <v>115</v>
       </c>
@@ -90151,68 +90151,68 @@
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
